--- a/df_fPC1/sum.var_AMR_ville_FQ_R.xlsx
+++ b/df_fPC1/sum.var_AMR_ville_FQ_R.xlsx
@@ -803,7 +803,7 @@
         <v>-0.0519636488636131</v>
       </c>
       <c r="J2" t="n">
-        <v>0.10036063159044</v>
+        <v>0.103147603373179</v>
       </c>
       <c r="K2" t="n">
         <v>0.0335610808107989</v>
@@ -1003,7 +1003,7 @@
         <v>0.0110822982171971</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0352159793973484</v>
+        <v>0.0332841500048817</v>
       </c>
       <c r="K3" t="n">
         <v>-0.0975259174762126</v>
@@ -1203,7 +1203,7 @@
         <v>-0.0181058995709713</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.278648268623139</v>
+        <v>-0.288815238863085</v>
       </c>
       <c r="K4" t="n">
         <v>-0.37338220636912</v>
@@ -1403,7 +1403,7 @@
         <v>-0.0943666974336294</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.046366232871423</v>
+        <v>-0.0408288727958792</v>
       </c>
       <c r="K5" t="n">
         <v>-0.130678648965293</v>
@@ -1603,7 +1603,7 @@
         <v>-0.00777819389424965</v>
       </c>
       <c r="J6" t="n">
-        <v>0.183072132285433</v>
+        <v>0.183906858976229</v>
       </c>
       <c r="K6" t="n">
         <v>-0.0140515295826258</v>
@@ -1803,7 +1803,7 @@
         <v>0.0918115939259928</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0601744798308835</v>
+        <v>0.0530386693634788</v>
       </c>
       <c r="K7" t="n">
         <v>-0.188331569638821</v>
@@ -2003,7 +2003,7 @@
         <v>-0.0493917054781802</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0883645155060498</v>
+        <v>-0.0853534747701536</v>
       </c>
       <c r="K8" t="n">
         <v>0.309219299525867</v>
@@ -2203,7 +2203,7 @@
         <v>0.0855536155303945</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0504734259398501</v>
+        <v>0.0546274119630951</v>
       </c>
       <c r="K9" t="n">
         <v>-0.208271122741779</v>
@@ -2403,7 +2403,7 @@
         <v>0.0705558338791445</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0849547857042242</v>
+        <v>0.0851385988275439</v>
       </c>
       <c r="K10" t="n">
         <v>0.0601430323680632</v>
@@ -2603,7 +2603,7 @@
         <v>0.0296954906944263</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0158617624856274</v>
+        <v>0.0110290195894473</v>
       </c>
       <c r="K11" t="n">
         <v>0.313060253546427</v>
@@ -2803,7 +2803,7 @@
         <v>0.0663592388653425</v>
       </c>
       <c r="J12" t="n">
-        <v>0.12082021118173</v>
+        <v>0.126087432551128</v>
       </c>
       <c r="K12" t="n">
         <v>0.467253145695357</v>
@@ -3003,7 +3003,7 @@
         <v>-0.133451925871853</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.237554391414924</v>
+        <v>-0.235262158219865</v>
       </c>
       <c r="K13" t="n">
         <v>-0.170995817172662</v>
